--- a/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
+++ b/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CE066A-B604-4B1D-8632-3E780A2FC1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A73B1A-16D0-4630-9137-8ABDEA9D7633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>

--- a/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
+++ b/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A73B1A-16D0-4630-9137-8ABDEA9D7633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384D7F0F-5E47-4890-A131-82022F581EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
+++ b/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384D7F0F-5E47-4890-A131-82022F581EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8262B986-97E1-400B-8D4B-AC1DABF29780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
+++ b/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8262B986-97E1-400B-8D4B-AC1DABF29780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29608163-8216-4F4D-AA77-5EF88EC9604E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
+++ b/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
@@ -2,26 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29608163-8216-4F4D-AA77-5EF88EC9604E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A7356E-2A90-4562-8F12-BDF2EB772E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
-    <sheet name="geo_sets" sheetId="5" r:id="rId2"/>
-    <sheet name="VEDA_Sets-Proc" sheetId="4" r:id="rId3"/>
+    <sheet name="VEDA_Sets-Comm" sheetId="1" r:id="rId1"/>
+    <sheet name="geo_sets" sheetId="2" r:id="rId2"/>
+    <sheet name="VEDA_Sets-Proc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,6 +37,129 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="941">
   <si>
+    <t>~TFM_Csets</t>
+  </si>
+  <si>
+    <t>CSET_SET</t>
+  </si>
+  <si>
+    <t>CSET_CN</t>
+  </si>
+  <si>
+    <t>CSET_CD</t>
+  </si>
+  <si>
+    <t>SetName</t>
+  </si>
+  <si>
+    <t>SetDesc</t>
+  </si>
+  <si>
+    <t>c_Pos_AndOr</t>
+  </si>
+  <si>
+    <t>c_Neg_AndOr</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>e*spv*</t>
+  </si>
+  <si>
+    <t>Solar elec</t>
+  </si>
+  <si>
+    <t>e*won*,e*wof*</t>
+  </si>
+  <si>
+    <t>Wind elec</t>
+  </si>
+  <si>
+    <t>coal,gas,oil</t>
+  </si>
+  <si>
+    <t>fossil</t>
+  </si>
+  <si>
+    <t>geothermal,hydro,solar,wind</t>
+  </si>
+  <si>
+    <t>renewable</t>
+  </si>
+  <si>
+    <t>bioenergy</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>elc_buildings</t>
+  </si>
+  <si>
+    <t>buildings</t>
+  </si>
+  <si>
+    <t>elc_industry</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>elc_transport</t>
+  </si>
+  <si>
+    <t>transport</t>
+  </si>
+  <si>
+    <t>elc_roadtransport</t>
+  </si>
+  <si>
+    <t>EVs</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>co2captured,co2[_]*</t>
+  </si>
+  <si>
+    <t>CO2Captured</t>
+  </si>
+  <si>
+    <t>co2s[_]*</t>
+  </si>
+  <si>
+    <t>CO2Stored</t>
+  </si>
+  <si>
+    <t>~tfm_psets</t>
+  </si>
+  <si>
+    <t>setname</t>
+  </si>
+  <si>
+    <t>pset_co</t>
+  </si>
+  <si>
+    <t>pset_ci</t>
+  </si>
+  <si>
+    <t>t_pos_andor</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
     <t>~TFM_Psets</t>
   </si>
   <si>
@@ -58,463 +178,340 @@
     <t>PSET_CO</t>
   </si>
   <si>
-    <t>SetName</t>
-  </si>
-  <si>
-    <t>SetDesc</t>
-  </si>
-  <si>
     <t>T_Pos_AndOr</t>
   </si>
   <si>
     <t>T_Neg_AndOr</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>ELE</t>
   </si>
   <si>
-    <t>~TFM_Csets</t>
-  </si>
-  <si>
-    <t>CSET_SET</t>
-  </si>
-  <si>
-    <t>CSET_CN</t>
-  </si>
-  <si>
-    <t>CSET_CD</t>
-  </si>
-  <si>
-    <t>c_Pos_AndOr</t>
-  </si>
-  <si>
-    <t>c_Neg_AndOr</t>
+    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*,*ember</t>
+  </si>
+  <si>
+    <t>gas,elcnga,elcgas,oil,elco</t>
   </si>
   <si>
     <t>CCGT</t>
   </si>
   <si>
+    <t>Combined Cycle Gas Turbine</t>
+  </si>
+  <si>
+    <t>Ramp ~8%/min</t>
+  </si>
+  <si>
+    <t>EP_GAS-GT*,EP_OIL-GT*,*gas_turbine*,EN*CT*</t>
+  </si>
+  <si>
+    <t>OCGT</t>
+  </si>
+  <si>
+    <t>Open Cycle Gas Turbine (Peaker)</t>
+  </si>
+  <si>
+    <t>Ramp ~15%/min</t>
+  </si>
+  <si>
+    <t>EP_GAS-ST*,EP_OIL-ST*,*steam*</t>
+  </si>
+  <si>
+    <t>Gas_Oil_Steam</t>
+  </si>
+  <si>
+    <t>Gas/Oil Steam Turbine</t>
+  </si>
+  <si>
+    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*,*internal_comb*</t>
+  </si>
+  <si>
+    <t>Int_Comb</t>
+  </si>
+  <si>
+    <t>Internal Combustion Engine</t>
+  </si>
+  <si>
+    <t>EP_COA-ST*,EP_LIG-ST*,*-CFB*,*coal_st*,*coal_subcritical*</t>
+  </si>
+  <si>
+    <t>coal,elcco*</t>
+  </si>
+  <si>
+    <t>Subcrit_Coal</t>
+  </si>
+  <si>
     <t>Subcritical Coal</t>
   </si>
   <si>
+    <t>Ramp ~3%/min</t>
+  </si>
+  <si>
+    <t>EP_COA-SC*,EP_COA-USC*,EP_LIG-SC*,EP_LIG-USC*,*coal_sc*,*coal_usc*,*coal_supercritical*,*coal_ultrasupercritical*</t>
+  </si>
+  <si>
+    <t>Supercrit_Coal</t>
+  </si>
+  <si>
+    <t>Supercritical/Ultra-Supercritical Coal</t>
+  </si>
+  <si>
+    <t>Ramp ~4%/min</t>
+  </si>
+  <si>
+    <t>*-IGCC*,*coal_igcc*</t>
+  </si>
+  <si>
+    <t>IGCC</t>
+  </si>
+  <si>
+    <t>Integrated Gasification CC</t>
+  </si>
+  <si>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>CHP_Gas</t>
+  </si>
+  <si>
+    <t>Gas/Oil CHP</t>
+  </si>
+  <si>
+    <t>Same ramp as ELE counterpart</t>
+  </si>
+  <si>
+    <t>CHP_Coal</t>
+  </si>
+  <si>
+    <t>Coal CHP</t>
+  </si>
+  <si>
+    <t>bio*,elcb*</t>
+  </si>
+  <si>
+    <t>CHP_Bio</t>
+  </si>
+  <si>
+    <t>Biomass CHP</t>
+  </si>
+  <si>
+    <t>HPL</t>
+  </si>
+  <si>
+    <t>HOP_Gas</t>
+  </si>
+  <si>
+    <t>Gas/Oil Heat-Only Boiler</t>
+  </si>
+  <si>
+    <t>HOP_Bio</t>
+  </si>
+  <si>
+    <t>Biomass Heat-Only Boiler</t>
+  </si>
+  <si>
+    <t>-*HP*</t>
+  </si>
+  <si>
+    <t>elc,e[_]*</t>
+  </si>
+  <si>
+    <t>HOP_Elec</t>
+  </si>
+  <si>
+    <t>Electric Boiler (DH)</t>
+  </si>
+  <si>
+    <t>*HP*</t>
+  </si>
+  <si>
+    <t>Heat_Pump</t>
+  </si>
+  <si>
+    <t>Large-Scale Heat Pump</t>
+  </si>
+  <si>
+    <t>Bio_Power</t>
+  </si>
+  <si>
+    <t>Biomass Power (ELE)</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>elcs*,solar</t>
+  </si>
+  <si>
+    <t>Solar_Util</t>
+  </si>
+  <si>
+    <t>Solar Utility</t>
+  </si>
+  <si>
+    <t>elcwin,windon</t>
+  </si>
+  <si>
+    <t>Wind_Onshore</t>
+  </si>
+  <si>
+    <t>Wind Onshore</t>
+  </si>
+  <si>
+    <t>windoff</t>
+  </si>
+  <si>
+    <t>Wind_Offshore</t>
+  </si>
+  <si>
+    <t>Wind Offshore</t>
+  </si>
+  <si>
+    <t>elcgeo,geothermal</t>
+  </si>
+  <si>
+    <t>Geothermal</t>
+  </si>
+  <si>
+    <t>Geothermal Power</t>
+  </si>
+  <si>
+    <t>-*ror*</t>
+  </si>
+  <si>
+    <t>elchyd,hydro</t>
+  </si>
+  <si>
+    <t>Hydro_Dam</t>
+  </si>
+  <si>
+    <t>Hydro Dam</t>
+  </si>
+  <si>
+    <t>And</t>
+  </si>
+  <si>
+    <t>Or</t>
+  </si>
+  <si>
+    <t>*HYD-ROR*,*ror*</t>
+  </si>
+  <si>
+    <t>Hydro_RoR</t>
+  </si>
+  <si>
+    <t>Hydro Run-of-River</t>
+  </si>
+  <si>
+    <t>-*SMR*</t>
+  </si>
+  <si>
+    <t>elcnuc,nuclear</t>
+  </si>
+  <si>
+    <t>Nuclear_P</t>
+  </si>
+  <si>
+    <t>Nuclear (Conventional)</t>
+  </si>
+  <si>
+    <t>*SMR*</t>
+  </si>
+  <si>
+    <t>Nuclear_SMR</t>
+  </si>
+  <si>
+    <t>Nuclear SMR</t>
+  </si>
+  <si>
     <t>STG</t>
   </si>
   <si>
-    <t>IGCC</t>
+    <t>*HPS*,*hydro_ps*</t>
+  </si>
+  <si>
+    <t>Hydro_PS</t>
+  </si>
+  <si>
+    <t>Pumped Hydro Storage</t>
+  </si>
+  <si>
+    <t>*4h*,*8h*,*12h*,-*EV*</t>
+  </si>
+  <si>
+    <t>Batt_Util</t>
+  </si>
+  <si>
+    <t>Utility Battery Storage</t>
   </si>
   <si>
     <t>*EV*</t>
   </si>
   <si>
+    <t>Batt_EV</t>
+  </si>
+  <si>
+    <t>EV Battery</t>
+  </si>
+  <si>
+    <t>IRE</t>
+  </si>
+  <si>
+    <t>g[_]*</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>DMD</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>stepdown*</t>
+  </si>
+  <si>
+    <t>Transformers Dn</t>
+  </si>
+  <si>
+    <t>stepup*</t>
+  </si>
+  <si>
+    <t>Transformers Up</t>
+  </si>
+  <si>
+    <t>distr*</t>
+  </si>
+  <si>
+    <t>Aggregators</t>
+  </si>
+  <si>
+    <t>IMP*Z</t>
+  </si>
+  <si>
+    <t>DUMMY_IMP</t>
+  </si>
+  <si>
+    <t>distr_sol*</t>
+  </si>
+  <si>
+    <t>distr_won*</t>
+  </si>
+  <si>
+    <t>distr_wof*</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
     <t>hydro</t>
   </si>
   <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>And</t>
-  </si>
-  <si>
-    <t>Or</t>
-  </si>
-  <si>
-    <t>Grid</t>
-  </si>
-  <si>
-    <t>IRE</t>
-  </si>
-  <si>
-    <t>g[_]*</t>
-  </si>
-  <si>
-    <t>DMD</t>
-  </si>
-  <si>
-    <t>Demand</t>
-  </si>
-  <si>
-    <t>e*spv*</t>
-  </si>
-  <si>
-    <t>e*won*,e*wof*</t>
-  </si>
-  <si>
-    <t>bioenergy</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>elc_buildings</t>
-  </si>
-  <si>
-    <t>elc_industry</t>
-  </si>
-  <si>
-    <t>elc_transport</t>
-  </si>
-  <si>
-    <t>elc_roadtransport</t>
-  </si>
-  <si>
-    <t>co2</t>
-  </si>
-  <si>
-    <t>buildings</t>
-  </si>
-  <si>
-    <t>industry</t>
-  </si>
-  <si>
-    <t>transport</t>
-  </si>
-  <si>
-    <t>EVs</t>
-  </si>
-  <si>
-    <t>fossil</t>
-  </si>
-  <si>
-    <t>coal,gas,oil</t>
-  </si>
-  <si>
-    <t>geothermal,hydro,solar,wind</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>stepdown*</t>
-  </si>
-  <si>
-    <t>Nuclear SMR</t>
-  </si>
-  <si>
-    <t>*SMR*</t>
-  </si>
-  <si>
-    <t>-*SMR*</t>
-  </si>
-  <si>
-    <t>Hydro Dam</t>
-  </si>
-  <si>
-    <t>renewable</t>
-  </si>
-  <si>
-    <t>Solar elec</t>
-  </si>
-  <si>
-    <t>Wind elec</t>
-  </si>
-  <si>
-    <t>Aggregators</t>
-  </si>
-  <si>
-    <t>IMP*Z</t>
-  </si>
-  <si>
-    <t>DUMMY_IMP</t>
-  </si>
-  <si>
-    <t>stepup*</t>
-  </si>
-  <si>
-    <t>Transformers Up</t>
-  </si>
-  <si>
-    <t>Transformers Dn</t>
-  </si>
-  <si>
-    <t>windoff</t>
-  </si>
-  <si>
-    <t>distr*</t>
-  </si>
-  <si>
-    <t>ELE,CHP</t>
-  </si>
-  <si>
-    <t>distr_sol*</t>
-  </si>
-  <si>
-    <t>distr_won*</t>
-  </si>
-  <si>
-    <t>distr_wof*</t>
-  </si>
-  <si>
     <t>coal</t>
-  </si>
-  <si>
-    <t>*4h*,*8h*,*12h*,-*EV*</t>
-  </si>
-  <si>
-    <t>Combined Cycle Gas Turbine</t>
-  </si>
-  <si>
-    <t>Ramp ~8%/min</t>
-  </si>
-  <si>
-    <t>OCGT</t>
-  </si>
-  <si>
-    <t>Open Cycle Gas Turbine (Peaker)</t>
-  </si>
-  <si>
-    <t>Ramp ~15%/min</t>
-  </si>
-  <si>
-    <t>Gas_Oil_Steam</t>
-  </si>
-  <si>
-    <t>Gas/Oil Steam Turbine</t>
-  </si>
-  <si>
-    <t>Int_Comb</t>
-  </si>
-  <si>
-    <t>Internal Combustion Engine</t>
-  </si>
-  <si>
-    <t>Subcrit_Coal</t>
-  </si>
-  <si>
-    <t>Ramp ~3%/min</t>
-  </si>
-  <si>
-    <t>Supercrit_Coal</t>
-  </si>
-  <si>
-    <t>Supercritical/Ultra-Supercritical Coal</t>
-  </si>
-  <si>
-    <t>Ramp ~4%/min</t>
-  </si>
-  <si>
-    <t>*-IGCC*,*coal_igcc*</t>
-  </si>
-  <si>
-    <t>Integrated Gasification CC</t>
-  </si>
-  <si>
-    <t>CHP</t>
-  </si>
-  <si>
-    <t>CHP_Gas</t>
-  </si>
-  <si>
-    <t>Gas/Oil CHP</t>
-  </si>
-  <si>
-    <t>Same ramp as ELE counterpart</t>
-  </si>
-  <si>
-    <t>CHP_Coal</t>
-  </si>
-  <si>
-    <t>Coal CHP</t>
-  </si>
-  <si>
-    <t>CHP_Bio</t>
-  </si>
-  <si>
-    <t>Biomass CHP</t>
-  </si>
-  <si>
-    <t>HPL</t>
-  </si>
-  <si>
-    <t>HOP_Gas</t>
-  </si>
-  <si>
-    <t>Gas/Oil Heat-Only Boiler</t>
-  </si>
-  <si>
-    <t>HOP_Bio</t>
-  </si>
-  <si>
-    <t>Biomass Heat-Only Boiler</t>
-  </si>
-  <si>
-    <t>HOP_Elec</t>
-  </si>
-  <si>
-    <t>Electric Boiler (DH)</t>
-  </si>
-  <si>
-    <t>Heat_Pump</t>
-  </si>
-  <si>
-    <t>Large-Scale Heat Pump</t>
-  </si>
-  <si>
-    <t>Bio_Power</t>
-  </si>
-  <si>
-    <t>Biomass Power (ELE)</t>
-  </si>
-  <si>
-    <t>elcs*,solar</t>
-  </si>
-  <si>
-    <t>Solar_Util</t>
-  </si>
-  <si>
-    <t>Solar Utility</t>
-  </si>
-  <si>
-    <t>elcwin,windon</t>
-  </si>
-  <si>
-    <t>Wind_Onshore</t>
-  </si>
-  <si>
-    <t>Wind Onshore</t>
-  </si>
-  <si>
-    <t>Wind_Offshore</t>
-  </si>
-  <si>
-    <t>Wind Offshore</t>
-  </si>
-  <si>
-    <t>elcgeo,geothermal</t>
-  </si>
-  <si>
-    <t>Geothermal</t>
-  </si>
-  <si>
-    <t>Geothermal Power</t>
-  </si>
-  <si>
-    <t>elchyd,hydro</t>
-  </si>
-  <si>
-    <t>Hydro_Dam</t>
-  </si>
-  <si>
-    <t>*HYD-ROR*,*ror*</t>
-  </si>
-  <si>
-    <t>Hydro_RoR</t>
-  </si>
-  <si>
-    <t>Hydro Run-of-River</t>
-  </si>
-  <si>
-    <t>elcnuc,nuclear</t>
-  </si>
-  <si>
-    <t>Nuclear (Conventional)</t>
-  </si>
-  <si>
-    <t>Nuclear_SMR</t>
-  </si>
-  <si>
-    <t>*HPS*,*hydro_ps*</t>
-  </si>
-  <si>
-    <t>Hydro_PS</t>
-  </si>
-  <si>
-    <t>Pumped Hydro Storage</t>
-  </si>
-  <si>
-    <t>Batt_Util</t>
-  </si>
-  <si>
-    <t>Utility Battery Storage</t>
-  </si>
-  <si>
-    <t>Batt_EV</t>
-  </si>
-  <si>
-    <t>EV Battery</t>
-  </si>
-  <si>
-    <t>EP_GAS-GT*,EP_OIL-GT*,*gas_turbine*,EN*CT*</t>
-  </si>
-  <si>
-    <t>EP_COA-ST*,EP_LIG-ST*,*-CFB*,*coal_subcritical*</t>
-  </si>
-  <si>
-    <t>co2captured,co2[_]*</t>
-  </si>
-  <si>
-    <t>CO2Captured</t>
-  </si>
-  <si>
-    <t>co2s[_]*</t>
-  </si>
-  <si>
-    <t>CO2Stored</t>
-  </si>
-  <si>
-    <t>ELC,e[_]*</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Nuclear_P</t>
-  </si>
-  <si>
-    <t>~tfm_psets</t>
-  </si>
-  <si>
-    <t>setname</t>
-  </si>
-  <si>
-    <t>pset_co</t>
-  </si>
-  <si>
-    <t>pset_ci</t>
-  </si>
-  <si>
-    <t>t_pos_andor</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>-*ror*</t>
-  </si>
-  <si>
-    <t>EP_COA-SC*,EP_COA-USC*,EP_LIG-SC*,EP_LIG-USC*,*critical*</t>
-  </si>
-  <si>
-    <t>coal,elcco*</t>
-  </si>
-  <si>
-    <t>gas,elcnga,elcgas,oil,elco</t>
-  </si>
-  <si>
-    <t>bio*,elcb*</t>
-  </si>
-  <si>
-    <t>*HP*</t>
-  </si>
-  <si>
-    <t>-*HP*</t>
-  </si>
-  <si>
-    <t>elc,e[_]*</t>
-  </si>
-  <si>
-    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*,*internal_comb*</t>
-  </si>
-  <si>
-    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*,*ember</t>
-  </si>
-  <si>
-    <t>EP_GAS-ST*,EP_OIL-ST*,*steam*</t>
   </si>
   <si>
     <t>p_Shanghai_CHN</t>
@@ -2935,8 +2932,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2964,9 +2961,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3004,7 +3001,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3110,7 +3107,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3252,14 +3249,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB068F12-506D-4B74-BF24-03EBDA23C84D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3276,70 +3273,70 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D7" t="str">
         <f>B7</f>
@@ -3348,7 +3345,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D8" t="str">
         <f>B8</f>
@@ -3357,7 +3354,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D9" t="str">
         <f>B9</f>
@@ -3366,47 +3363,47 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D15" t="str">
         <f>B15</f>
@@ -3415,50 +3412,47 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D16">
-    <sortCondition ref="A5:A16"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9596CD-0528-4380-8F2D-D99C9A838BA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B9:E401"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
@@ -3472,7 +3466,7 @@
         <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
@@ -3486,7 +3480,7 @@
         <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
@@ -3500,7 +3494,7 @@
         <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -3514,7 +3508,7 @@
         <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
@@ -3528,7 +3522,7 @@
         <v>168</v>
       </c>
       <c r="E15" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -3542,7 +3536,7 @@
         <v>170</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -3556,7 +3550,7 @@
         <v>172</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
@@ -3570,7 +3564,7 @@
         <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
@@ -3584,7 +3578,7 @@
         <v>176</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
@@ -3598,7 +3592,7 @@
         <v>178</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
@@ -3612,7 +3606,7 @@
         <v>180</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
@@ -3626,7 +3620,7 @@
         <v>182</v>
       </c>
       <c r="E22" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
@@ -3640,7 +3634,7 @@
         <v>184</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
@@ -3654,7 +3648,7 @@
         <v>186</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -3668,7 +3662,7 @@
         <v>188</v>
       </c>
       <c r="E25" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
@@ -3682,7 +3676,7 @@
         <v>190</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
@@ -3696,7 +3690,7 @@
         <v>192</v>
       </c>
       <c r="E27" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
@@ -3710,7 +3704,7 @@
         <v>194</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
@@ -3724,7 +3718,7 @@
         <v>196</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
@@ -3738,7 +3732,7 @@
         <v>198</v>
       </c>
       <c r="E30" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
@@ -3752,7 +3746,7 @@
         <v>200</v>
       </c>
       <c r="E31" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
@@ -3766,7 +3760,7 @@
         <v>202</v>
       </c>
       <c r="E32" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
@@ -3780,7 +3774,7 @@
         <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
@@ -3794,7 +3788,7 @@
         <v>206</v>
       </c>
       <c r="E34" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
@@ -3808,7 +3802,7 @@
         <v>208</v>
       </c>
       <c r="E35" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
@@ -3822,7 +3816,7 @@
         <v>210</v>
       </c>
       <c r="E36" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
@@ -3836,7 +3830,7 @@
         <v>212</v>
       </c>
       <c r="E37" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
@@ -3850,7 +3844,7 @@
         <v>214</v>
       </c>
       <c r="E38" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
@@ -3864,7 +3858,7 @@
         <v>216</v>
       </c>
       <c r="E39" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
@@ -3878,7 +3872,7 @@
         <v>218</v>
       </c>
       <c r="E40" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
@@ -3892,7 +3886,7 @@
         <v>220</v>
       </c>
       <c r="E41" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
@@ -3906,7 +3900,7 @@
         <v>222</v>
       </c>
       <c r="E42" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
@@ -3920,7 +3914,7 @@
         <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
@@ -3934,7 +3928,7 @@
         <v>226</v>
       </c>
       <c r="E44" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
@@ -3948,7 +3942,7 @@
         <v>228</v>
       </c>
       <c r="E45" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
@@ -3962,7 +3956,7 @@
         <v>230</v>
       </c>
       <c r="E46" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
@@ -3976,7 +3970,7 @@
         <v>232</v>
       </c>
       <c r="E47" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
@@ -3990,7 +3984,7 @@
         <v>234</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -4004,7 +3998,7 @@
         <v>236</v>
       </c>
       <c r="E49" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
@@ -4018,7 +4012,7 @@
         <v>238</v>
       </c>
       <c r="E50" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
@@ -4032,7 +4026,7 @@
         <v>240</v>
       </c>
       <c r="E51" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
@@ -4046,7 +4040,7 @@
         <v>242</v>
       </c>
       <c r="E52" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
@@ -4060,7 +4054,7 @@
         <v>244</v>
       </c>
       <c r="E53" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
@@ -4074,7 +4068,7 @@
         <v>246</v>
       </c>
       <c r="E54" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
@@ -4088,7 +4082,7 @@
         <v>248</v>
       </c>
       <c r="E55" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
@@ -4102,7 +4096,7 @@
         <v>250</v>
       </c>
       <c r="E56" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
@@ -4116,7 +4110,7 @@
         <v>252</v>
       </c>
       <c r="E57" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
@@ -4130,7 +4124,7 @@
         <v>254</v>
       </c>
       <c r="E58" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
@@ -4144,7 +4138,7 @@
         <v>256</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
@@ -4158,7 +4152,7 @@
         <v>258</v>
       </c>
       <c r="E60" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
@@ -4172,7 +4166,7 @@
         <v>260</v>
       </c>
       <c r="E61" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
@@ -4186,7 +4180,7 @@
         <v>262</v>
       </c>
       <c r="E62" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
@@ -4200,7 +4194,7 @@
         <v>264</v>
       </c>
       <c r="E63" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
@@ -4214,7 +4208,7 @@
         <v>266</v>
       </c>
       <c r="E64" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
@@ -4228,7 +4222,7 @@
         <v>268</v>
       </c>
       <c r="E65" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
@@ -4242,7 +4236,7 @@
         <v>270</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
@@ -4256,7 +4250,7 @@
         <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
@@ -4270,7 +4264,7 @@
         <v>274</v>
       </c>
       <c r="E68" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
@@ -4284,7 +4278,7 @@
         <v>276</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
@@ -4298,7 +4292,7 @@
         <v>278</v>
       </c>
       <c r="E70" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
@@ -4312,7 +4306,7 @@
         <v>280</v>
       </c>
       <c r="E71" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
@@ -4326,7 +4320,7 @@
         <v>282</v>
       </c>
       <c r="E72" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
@@ -4340,7 +4334,7 @@
         <v>284</v>
       </c>
       <c r="E73" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
@@ -4354,7 +4348,7 @@
         <v>286</v>
       </c>
       <c r="E74" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
@@ -4368,7 +4362,7 @@
         <v>288</v>
       </c>
       <c r="E75" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
@@ -4382,7 +4376,7 @@
         <v>290</v>
       </c>
       <c r="E76" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
@@ -4396,7 +4390,7 @@
         <v>292</v>
       </c>
       <c r="E77" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
@@ -4410,7 +4404,7 @@
         <v>294</v>
       </c>
       <c r="E78" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
@@ -4424,7 +4418,7 @@
         <v>296</v>
       </c>
       <c r="E79" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
@@ -4438,7 +4432,7 @@
         <v>298</v>
       </c>
       <c r="E80" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
@@ -4452,7 +4446,7 @@
         <v>300</v>
       </c>
       <c r="E81" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
@@ -4466,7 +4460,7 @@
         <v>302</v>
       </c>
       <c r="E82" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
@@ -4480,7 +4474,7 @@
         <v>304</v>
       </c>
       <c r="E83" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
@@ -4494,7 +4488,7 @@
         <v>306</v>
       </c>
       <c r="E84" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
@@ -4508,7 +4502,7 @@
         <v>308</v>
       </c>
       <c r="E85" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
@@ -4522,7 +4516,7 @@
         <v>310</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
@@ -4536,7 +4530,7 @@
         <v>312</v>
       </c>
       <c r="E87" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
@@ -4550,7 +4544,7 @@
         <v>314</v>
       </c>
       <c r="E88" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
@@ -4564,7 +4558,7 @@
         <v>316</v>
       </c>
       <c r="E89" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
@@ -4578,7 +4572,7 @@
         <v>318</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
@@ -4592,7 +4586,7 @@
         <v>320</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
@@ -4606,7 +4600,7 @@
         <v>322</v>
       </c>
       <c r="E92" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
@@ -4620,7 +4614,7 @@
         <v>324</v>
       </c>
       <c r="E93" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
@@ -4634,7 +4628,7 @@
         <v>326</v>
       </c>
       <c r="E94" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
@@ -4648,7 +4642,7 @@
         <v>328</v>
       </c>
       <c r="E95" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
@@ -4662,7 +4656,7 @@
         <v>330</v>
       </c>
       <c r="E96" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
@@ -4676,7 +4670,7 @@
         <v>332</v>
       </c>
       <c r="E97" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
@@ -4690,7 +4684,7 @@
         <v>334</v>
       </c>
       <c r="E98" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
@@ -4704,7 +4698,7 @@
         <v>336</v>
       </c>
       <c r="E99" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.45">
@@ -4718,7 +4712,7 @@
         <v>338</v>
       </c>
       <c r="E100" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.45">
@@ -4732,7 +4726,7 @@
         <v>340</v>
       </c>
       <c r="E101" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.45">
@@ -4746,7 +4740,7 @@
         <v>342</v>
       </c>
       <c r="E102" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.45">
@@ -4760,7 +4754,7 @@
         <v>344</v>
       </c>
       <c r="E103" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.45">
@@ -4774,7 +4768,7 @@
         <v>346</v>
       </c>
       <c r="E104" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.45">
@@ -4788,7 +4782,7 @@
         <v>348</v>
       </c>
       <c r="E105" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.45">
@@ -4802,7 +4796,7 @@
         <v>350</v>
       </c>
       <c r="E106" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.45">
@@ -4816,7 +4810,7 @@
         <v>352</v>
       </c>
       <c r="E107" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.45">
@@ -4830,7 +4824,7 @@
         <v>354</v>
       </c>
       <c r="E108" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.45">
@@ -4844,7 +4838,7 @@
         <v>356</v>
       </c>
       <c r="E109" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.45">
@@ -4858,7 +4852,7 @@
         <v>358</v>
       </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.45">
@@ -4872,7 +4866,7 @@
         <v>360</v>
       </c>
       <c r="E111" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.45">
@@ -4886,7 +4880,7 @@
         <v>362</v>
       </c>
       <c r="E112" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.45">
@@ -4900,7 +4894,7 @@
         <v>364</v>
       </c>
       <c r="E113" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.45">
@@ -4914,7 +4908,7 @@
         <v>366</v>
       </c>
       <c r="E114" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.45">
@@ -4928,7 +4922,7 @@
         <v>368</v>
       </c>
       <c r="E115" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.45">
@@ -4942,7 +4936,7 @@
         <v>370</v>
       </c>
       <c r="E116" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.45">
@@ -4956,7 +4950,7 @@
         <v>372</v>
       </c>
       <c r="E117" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.45">
@@ -4970,7 +4964,7 @@
         <v>374</v>
       </c>
       <c r="E118" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.45">
@@ -4984,7 +4978,7 @@
         <v>376</v>
       </c>
       <c r="E119" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.45">
@@ -4998,7 +4992,7 @@
         <v>378</v>
       </c>
       <c r="E120" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.45">
@@ -5012,7 +5006,7 @@
         <v>380</v>
       </c>
       <c r="E121" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.45">
@@ -5026,7 +5020,7 @@
         <v>382</v>
       </c>
       <c r="E122" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.45">
@@ -5040,7 +5034,7 @@
         <v>384</v>
       </c>
       <c r="E123" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.45">
@@ -5054,7 +5048,7 @@
         <v>386</v>
       </c>
       <c r="E124" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.45">
@@ -5068,7 +5062,7 @@
         <v>388</v>
       </c>
       <c r="E125" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.45">
@@ -5082,7 +5076,7 @@
         <v>390</v>
       </c>
       <c r="E126" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.45">
@@ -5096,7 +5090,7 @@
         <v>392</v>
       </c>
       <c r="E127" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.45">
@@ -5110,7 +5104,7 @@
         <v>394</v>
       </c>
       <c r="E128" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.45">
@@ -5124,7 +5118,7 @@
         <v>396</v>
       </c>
       <c r="E129" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.45">
@@ -5138,7 +5132,7 @@
         <v>398</v>
       </c>
       <c r="E130" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.45">
@@ -5152,7 +5146,7 @@
         <v>400</v>
       </c>
       <c r="E131" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.45">
@@ -5166,7 +5160,7 @@
         <v>402</v>
       </c>
       <c r="E132" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.45">
@@ -5180,7 +5174,7 @@
         <v>404</v>
       </c>
       <c r="E133" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.45">
@@ -5194,7 +5188,7 @@
         <v>406</v>
       </c>
       <c r="E134" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.45">
@@ -5208,7 +5202,7 @@
         <v>408</v>
       </c>
       <c r="E135" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.45">
@@ -5222,7 +5216,7 @@
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.45">
@@ -5236,7 +5230,7 @@
         <v>412</v>
       </c>
       <c r="E137" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.45">
@@ -5250,7 +5244,7 @@
         <v>414</v>
       </c>
       <c r="E138" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.45">
@@ -5264,7 +5258,7 @@
         <v>416</v>
       </c>
       <c r="E139" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.45">
@@ -5278,7 +5272,7 @@
         <v>418</v>
       </c>
       <c r="E140" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.45">
@@ -5292,7 +5286,7 @@
         <v>420</v>
       </c>
       <c r="E141" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.45">
@@ -5306,7 +5300,7 @@
         <v>422</v>
       </c>
       <c r="E142" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.45">
@@ -5320,7 +5314,7 @@
         <v>424</v>
       </c>
       <c r="E143" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.45">
@@ -5334,7 +5328,7 @@
         <v>426</v>
       </c>
       <c r="E144" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.45">
@@ -5348,7 +5342,7 @@
         <v>428</v>
       </c>
       <c r="E145" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.45">
@@ -5362,7 +5356,7 @@
         <v>430</v>
       </c>
       <c r="E146" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.45">
@@ -5376,7 +5370,7 @@
         <v>432</v>
       </c>
       <c r="E147" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.45">
@@ -5390,7 +5384,7 @@
         <v>434</v>
       </c>
       <c r="E148" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.45">
@@ -5404,7 +5398,7 @@
         <v>436</v>
       </c>
       <c r="E149" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.45">
@@ -5418,7 +5412,7 @@
         <v>438</v>
       </c>
       <c r="E150" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.45">
@@ -5432,7 +5426,7 @@
         <v>440</v>
       </c>
       <c r="E151" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.45">
@@ -5446,7 +5440,7 @@
         <v>442</v>
       </c>
       <c r="E152" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.45">
@@ -5460,7 +5454,7 @@
         <v>444</v>
       </c>
       <c r="E153" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.45">
@@ -5474,7 +5468,7 @@
         <v>446</v>
       </c>
       <c r="E154" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.45">
@@ -5488,7 +5482,7 @@
         <v>448</v>
       </c>
       <c r="E155" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.45">
@@ -5502,7 +5496,7 @@
         <v>450</v>
       </c>
       <c r="E156" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.45">
@@ -5516,7 +5510,7 @@
         <v>452</v>
       </c>
       <c r="E157" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.45">
@@ -5530,7 +5524,7 @@
         <v>454</v>
       </c>
       <c r="E158" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.45">
@@ -5544,7 +5538,7 @@
         <v>456</v>
       </c>
       <c r="E159" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.45">
@@ -5558,7 +5552,7 @@
         <v>458</v>
       </c>
       <c r="E160" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.45">
@@ -5572,7 +5566,7 @@
         <v>460</v>
       </c>
       <c r="E161" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.45">
@@ -5586,7 +5580,7 @@
         <v>462</v>
       </c>
       <c r="E162" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.45">
@@ -5600,7 +5594,7 @@
         <v>464</v>
       </c>
       <c r="E163" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.45">
@@ -5614,7 +5608,7 @@
         <v>466</v>
       </c>
       <c r="E164" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.45">
@@ -5628,7 +5622,7 @@
         <v>468</v>
       </c>
       <c r="E165" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.45">
@@ -5642,7 +5636,7 @@
         <v>470</v>
       </c>
       <c r="E166" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.45">
@@ -5656,7 +5650,7 @@
         <v>472</v>
       </c>
       <c r="E167" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.45">
@@ -5670,7 +5664,7 @@
         <v>474</v>
       </c>
       <c r="E168" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.45">
@@ -5684,7 +5678,7 @@
         <v>476</v>
       </c>
       <c r="E169" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.45">
@@ -5698,7 +5692,7 @@
         <v>478</v>
       </c>
       <c r="E170" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.45">
@@ -5712,7 +5706,7 @@
         <v>480</v>
       </c>
       <c r="E171" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.45">
@@ -5726,7 +5720,7 @@
         <v>482</v>
       </c>
       <c r="E172" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.45">
@@ -5740,7 +5734,7 @@
         <v>484</v>
       </c>
       <c r="E173" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.45">
@@ -5754,7 +5748,7 @@
         <v>486</v>
       </c>
       <c r="E174" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.45">
@@ -5768,7 +5762,7 @@
         <v>488</v>
       </c>
       <c r="E175" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.45">
@@ -5782,7 +5776,7 @@
         <v>490</v>
       </c>
       <c r="E176" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.45">
@@ -5796,7 +5790,7 @@
         <v>492</v>
       </c>
       <c r="E177" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.45">
@@ -5810,7 +5804,7 @@
         <v>494</v>
       </c>
       <c r="E178" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.45">
@@ -5824,7 +5818,7 @@
         <v>496</v>
       </c>
       <c r="E179" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.45">
@@ -5838,7 +5832,7 @@
         <v>498</v>
       </c>
       <c r="E180" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.45">
@@ -5852,7 +5846,7 @@
         <v>500</v>
       </c>
       <c r="E181" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.45">
@@ -5866,7 +5860,7 @@
         <v>502</v>
       </c>
       <c r="E182" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.45">
@@ -5880,7 +5874,7 @@
         <v>504</v>
       </c>
       <c r="E183" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.45">
@@ -5894,7 +5888,7 @@
         <v>506</v>
       </c>
       <c r="E184" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.45">
@@ -5908,7 +5902,7 @@
         <v>508</v>
       </c>
       <c r="E185" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.45">
@@ -5922,7 +5916,7 @@
         <v>510</v>
       </c>
       <c r="E186" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.45">
@@ -5936,7 +5930,7 @@
         <v>512</v>
       </c>
       <c r="E187" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.45">
@@ -5950,7 +5944,7 @@
         <v>514</v>
       </c>
       <c r="E188" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.45">
@@ -5964,7 +5958,7 @@
         <v>516</v>
       </c>
       <c r="E189" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.45">
@@ -5978,7 +5972,7 @@
         <v>518</v>
       </c>
       <c r="E190" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.45">
@@ -5992,7 +5986,7 @@
         <v>520</v>
       </c>
       <c r="E191" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.45">
@@ -6006,7 +6000,7 @@
         <v>522</v>
       </c>
       <c r="E192" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.45">
@@ -6020,7 +6014,7 @@
         <v>524</v>
       </c>
       <c r="E193" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.45">
@@ -6034,7 +6028,7 @@
         <v>526</v>
       </c>
       <c r="E194" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.45">
@@ -6048,7 +6042,7 @@
         <v>528</v>
       </c>
       <c r="E195" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.45">
@@ -6062,7 +6056,7 @@
         <v>530</v>
       </c>
       <c r="E196" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.45">
@@ -6076,7 +6070,7 @@
         <v>532</v>
       </c>
       <c r="E197" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.45">
@@ -6090,7 +6084,7 @@
         <v>534</v>
       </c>
       <c r="E198" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.45">
@@ -6104,7 +6098,7 @@
         <v>536</v>
       </c>
       <c r="E199" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.45">
@@ -6118,7 +6112,7 @@
         <v>538</v>
       </c>
       <c r="E200" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.45">
@@ -6132,7 +6126,7 @@
         <v>540</v>
       </c>
       <c r="E201" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.45">
@@ -6146,7 +6140,7 @@
         <v>542</v>
       </c>
       <c r="E202" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.45">
@@ -6160,7 +6154,7 @@
         <v>544</v>
       </c>
       <c r="E203" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.45">
@@ -6174,7 +6168,7 @@
         <v>546</v>
       </c>
       <c r="E204" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.45">
@@ -6188,7 +6182,7 @@
         <v>548</v>
       </c>
       <c r="E205" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="206" spans="2:5" x14ac:dyDescent="0.45">
@@ -6202,7 +6196,7 @@
         <v>550</v>
       </c>
       <c r="E206" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207" spans="2:5" x14ac:dyDescent="0.45">
@@ -6216,7 +6210,7 @@
         <v>552</v>
       </c>
       <c r="E207" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208" spans="2:5" x14ac:dyDescent="0.45">
@@ -6230,7 +6224,7 @@
         <v>554</v>
       </c>
       <c r="E208" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209" spans="2:5" x14ac:dyDescent="0.45">
@@ -6244,7 +6238,7 @@
         <v>556</v>
       </c>
       <c r="E209" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.45">
@@ -6258,7 +6252,7 @@
         <v>558</v>
       </c>
       <c r="E210" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="211" spans="2:5" x14ac:dyDescent="0.45">
@@ -6272,7 +6266,7 @@
         <v>560</v>
       </c>
       <c r="E211" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.45">
@@ -6286,7 +6280,7 @@
         <v>562</v>
       </c>
       <c r="E212" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="213" spans="2:5" x14ac:dyDescent="0.45">
@@ -6300,7 +6294,7 @@
         <v>564</v>
       </c>
       <c r="E213" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.45">
@@ -6314,7 +6308,7 @@
         <v>566</v>
       </c>
       <c r="E214" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.45">
@@ -6328,7 +6322,7 @@
         <v>568</v>
       </c>
       <c r="E215" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="216" spans="2:5" x14ac:dyDescent="0.45">
@@ -6342,7 +6336,7 @@
         <v>570</v>
       </c>
       <c r="E216" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217" spans="2:5" x14ac:dyDescent="0.45">
@@ -6356,7 +6350,7 @@
         <v>572</v>
       </c>
       <c r="E217" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="218" spans="2:5" x14ac:dyDescent="0.45">
@@ -6370,7 +6364,7 @@
         <v>574</v>
       </c>
       <c r="E218" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="219" spans="2:5" x14ac:dyDescent="0.45">
@@ -6384,7 +6378,7 @@
         <v>576</v>
       </c>
       <c r="E219" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.45">
@@ -6398,7 +6392,7 @@
         <v>578</v>
       </c>
       <c r="E220" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="221" spans="2:5" x14ac:dyDescent="0.45">
@@ -6412,7 +6406,7 @@
         <v>580</v>
       </c>
       <c r="E221" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="222" spans="2:5" x14ac:dyDescent="0.45">
@@ -6426,7 +6420,7 @@
         <v>582</v>
       </c>
       <c r="E222" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223" spans="2:5" x14ac:dyDescent="0.45">
@@ -6440,7 +6434,7 @@
         <v>584</v>
       </c>
       <c r="E223" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="224" spans="2:5" x14ac:dyDescent="0.45">
@@ -6454,7 +6448,7 @@
         <v>586</v>
       </c>
       <c r="E224" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.45">
@@ -6468,7 +6462,7 @@
         <v>588</v>
       </c>
       <c r="E225" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.45">
@@ -6482,7 +6476,7 @@
         <v>590</v>
       </c>
       <c r="E226" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.45">
@@ -6496,7 +6490,7 @@
         <v>592</v>
       </c>
       <c r="E227" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.45">
@@ -6510,7 +6504,7 @@
         <v>594</v>
       </c>
       <c r="E228" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.45">
@@ -6524,7 +6518,7 @@
         <v>596</v>
       </c>
       <c r="E229" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.45">
@@ -6538,7 +6532,7 @@
         <v>598</v>
       </c>
       <c r="E230" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="231" spans="2:5" x14ac:dyDescent="0.45">
@@ -6552,7 +6546,7 @@
         <v>600</v>
       </c>
       <c r="E231" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.45">
@@ -6566,7 +6560,7 @@
         <v>602</v>
       </c>
       <c r="E232" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.45">
@@ -6580,7 +6574,7 @@
         <v>604</v>
       </c>
       <c r="E233" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.45">
@@ -6594,7 +6588,7 @@
         <v>606</v>
       </c>
       <c r="E234" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.45">
@@ -6608,7 +6602,7 @@
         <v>608</v>
       </c>
       <c r="E235" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.45">
@@ -6622,7 +6616,7 @@
         <v>610</v>
       </c>
       <c r="E236" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.45">
@@ -6636,7 +6630,7 @@
         <v>612</v>
       </c>
       <c r="E237" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.45">
@@ -6650,7 +6644,7 @@
         <v>614</v>
       </c>
       <c r="E238" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.45">
@@ -6664,7 +6658,7 @@
         <v>616</v>
       </c>
       <c r="E239" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" spans="2:5" x14ac:dyDescent="0.45">
@@ -6678,7 +6672,7 @@
         <v>618</v>
       </c>
       <c r="E240" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.45">
@@ -6692,7 +6686,7 @@
         <v>620</v>
       </c>
       <c r="E241" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.45">
@@ -6706,7 +6700,7 @@
         <v>622</v>
       </c>
       <c r="E242" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.45">
@@ -6720,7 +6714,7 @@
         <v>624</v>
       </c>
       <c r="E243" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.45">
@@ -6734,7 +6728,7 @@
         <v>626</v>
       </c>
       <c r="E244" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.45">
@@ -6748,7 +6742,7 @@
         <v>628</v>
       </c>
       <c r="E245" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.45">
@@ -6762,7 +6756,7 @@
         <v>630</v>
       </c>
       <c r="E246" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.45">
@@ -6776,7 +6770,7 @@
         <v>632</v>
       </c>
       <c r="E247" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.45">
@@ -6790,7 +6784,7 @@
         <v>634</v>
       </c>
       <c r="E248" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.45">
@@ -6804,7 +6798,7 @@
         <v>636</v>
       </c>
       <c r="E249" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="250" spans="2:5" x14ac:dyDescent="0.45">
@@ -6818,7 +6812,7 @@
         <v>638</v>
       </c>
       <c r="E250" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251" spans="2:5" x14ac:dyDescent="0.45">
@@ -6832,7 +6826,7 @@
         <v>640</v>
       </c>
       <c r="E251" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.45">
@@ -6846,7 +6840,7 @@
         <v>642</v>
       </c>
       <c r="E252" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="253" spans="2:5" x14ac:dyDescent="0.45">
@@ -6860,7 +6854,7 @@
         <v>644</v>
       </c>
       <c r="E253" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.45">
@@ -6874,7 +6868,7 @@
         <v>646</v>
       </c>
       <c r="E254" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.45">
@@ -6888,7 +6882,7 @@
         <v>648</v>
       </c>
       <c r="E255" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.45">
@@ -6902,7 +6896,7 @@
         <v>650</v>
       </c>
       <c r="E256" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.45">
@@ -6916,7 +6910,7 @@
         <v>652</v>
       </c>
       <c r="E257" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.45">
@@ -6930,7 +6924,7 @@
         <v>654</v>
       </c>
       <c r="E258" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.45">
@@ -6944,7 +6938,7 @@
         <v>656</v>
       </c>
       <c r="E259" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.45">
@@ -6958,7 +6952,7 @@
         <v>658</v>
       </c>
       <c r="E260" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.45">
@@ -6972,7 +6966,7 @@
         <v>660</v>
       </c>
       <c r="E261" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.45">
@@ -6986,7 +6980,7 @@
         <v>662</v>
       </c>
       <c r="E262" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.45">
@@ -7000,7 +6994,7 @@
         <v>664</v>
       </c>
       <c r="E263" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.45">
@@ -7014,7 +7008,7 @@
         <v>666</v>
       </c>
       <c r="E264" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.45">
@@ -7028,7 +7022,7 @@
         <v>668</v>
       </c>
       <c r="E265" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.45">
@@ -7042,7 +7036,7 @@
         <v>670</v>
       </c>
       <c r="E266" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.45">
@@ -7056,7 +7050,7 @@
         <v>672</v>
       </c>
       <c r="E267" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.45">
@@ -7070,7 +7064,7 @@
         <v>674</v>
       </c>
       <c r="E268" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.45">
@@ -7084,7 +7078,7 @@
         <v>676</v>
       </c>
       <c r="E269" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.45">
@@ -7098,7 +7092,7 @@
         <v>678</v>
       </c>
       <c r="E270" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.45">
@@ -7112,7 +7106,7 @@
         <v>680</v>
       </c>
       <c r="E271" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.45">
@@ -7126,7 +7120,7 @@
         <v>682</v>
       </c>
       <c r="E272" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.45">
@@ -7140,7 +7134,7 @@
         <v>684</v>
       </c>
       <c r="E273" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.45">
@@ -7154,7 +7148,7 @@
         <v>686</v>
       </c>
       <c r="E274" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.45">
@@ -7168,7 +7162,7 @@
         <v>688</v>
       </c>
       <c r="E275" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.45">
@@ -7182,7 +7176,7 @@
         <v>690</v>
       </c>
       <c r="E276" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.45">
@@ -7196,7 +7190,7 @@
         <v>692</v>
       </c>
       <c r="E277" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.45">
@@ -7210,7 +7204,7 @@
         <v>694</v>
       </c>
       <c r="E278" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.45">
@@ -7224,7 +7218,7 @@
         <v>696</v>
       </c>
       <c r="E279" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.45">
@@ -7238,7 +7232,7 @@
         <v>698</v>
       </c>
       <c r="E280" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.45">
@@ -7252,7 +7246,7 @@
         <v>700</v>
       </c>
       <c r="E281" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.45">
@@ -7266,7 +7260,7 @@
         <v>702</v>
       </c>
       <c r="E282" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.45">
@@ -7280,7 +7274,7 @@
         <v>704</v>
       </c>
       <c r="E283" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.45">
@@ -7294,7 +7288,7 @@
         <v>706</v>
       </c>
       <c r="E284" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.45">
@@ -7308,7 +7302,7 @@
         <v>708</v>
       </c>
       <c r="E285" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.45">
@@ -7322,7 +7316,7 @@
         <v>710</v>
       </c>
       <c r="E286" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.45">
@@ -7336,7 +7330,7 @@
         <v>712</v>
       </c>
       <c r="E287" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.45">
@@ -7350,7 +7344,7 @@
         <v>714</v>
       </c>
       <c r="E288" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.45">
@@ -7364,7 +7358,7 @@
         <v>716</v>
       </c>
       <c r="E289" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.45">
@@ -7378,7 +7372,7 @@
         <v>718</v>
       </c>
       <c r="E290" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.45">
@@ -7392,7 +7386,7 @@
         <v>720</v>
       </c>
       <c r="E291" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.45">
@@ -7406,7 +7400,7 @@
         <v>722</v>
       </c>
       <c r="E292" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.45">
@@ -7420,7 +7414,7 @@
         <v>724</v>
       </c>
       <c r="E293" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.45">
@@ -7434,7 +7428,7 @@
         <v>726</v>
       </c>
       <c r="E294" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.45">
@@ -7448,7 +7442,7 @@
         <v>728</v>
       </c>
       <c r="E295" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.45">
@@ -7462,7 +7456,7 @@
         <v>730</v>
       </c>
       <c r="E296" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.45">
@@ -7476,7 +7470,7 @@
         <v>732</v>
       </c>
       <c r="E297" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.45">
@@ -7490,7 +7484,7 @@
         <v>734</v>
       </c>
       <c r="E298" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.45">
@@ -7504,7 +7498,7 @@
         <v>736</v>
       </c>
       <c r="E299" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.45">
@@ -7518,7 +7512,7 @@
         <v>738</v>
       </c>
       <c r="E300" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.45">
@@ -7532,7 +7526,7 @@
         <v>740</v>
       </c>
       <c r="E301" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.45">
@@ -7546,7 +7540,7 @@
         <v>742</v>
       </c>
       <c r="E302" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.45">
@@ -7560,7 +7554,7 @@
         <v>744</v>
       </c>
       <c r="E303" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.45">
@@ -7574,7 +7568,7 @@
         <v>746</v>
       </c>
       <c r="E304" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.45">
@@ -7588,7 +7582,7 @@
         <v>748</v>
       </c>
       <c r="E305" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.45">
@@ -7602,7 +7596,7 @@
         <v>750</v>
       </c>
       <c r="E306" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.45">
@@ -7616,7 +7610,7 @@
         <v>752</v>
       </c>
       <c r="E307" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.45">
@@ -7630,7 +7624,7 @@
         <v>754</v>
       </c>
       <c r="E308" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.45">
@@ -7644,7 +7638,7 @@
         <v>756</v>
       </c>
       <c r="E309" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.45">
@@ -7658,7 +7652,7 @@
         <v>758</v>
       </c>
       <c r="E310" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.45">
@@ -7672,7 +7666,7 @@
         <v>760</v>
       </c>
       <c r="E311" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.45">
@@ -7686,7 +7680,7 @@
         <v>762</v>
       </c>
       <c r="E312" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.45">
@@ -7700,7 +7694,7 @@
         <v>764</v>
       </c>
       <c r="E313" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.45">
@@ -7714,7 +7708,7 @@
         <v>766</v>
       </c>
       <c r="E314" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.45">
@@ -7728,7 +7722,7 @@
         <v>768</v>
       </c>
       <c r="E315" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.45">
@@ -7742,7 +7736,7 @@
         <v>770</v>
       </c>
       <c r="E316" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.45">
@@ -7756,7 +7750,7 @@
         <v>772</v>
       </c>
       <c r="E317" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.45">
@@ -7770,7 +7764,7 @@
         <v>774</v>
       </c>
       <c r="E318" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.45">
@@ -7784,7 +7778,7 @@
         <v>776</v>
       </c>
       <c r="E319" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.45">
@@ -7798,7 +7792,7 @@
         <v>778</v>
       </c>
       <c r="E320" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.45">
@@ -7812,7 +7806,7 @@
         <v>780</v>
       </c>
       <c r="E321" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.45">
@@ -7826,7 +7820,7 @@
         <v>782</v>
       </c>
       <c r="E322" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.45">
@@ -7840,7 +7834,7 @@
         <v>784</v>
       </c>
       <c r="E323" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.45">
@@ -7854,7 +7848,7 @@
         <v>786</v>
       </c>
       <c r="E324" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.45">
@@ -7868,7 +7862,7 @@
         <v>788</v>
       </c>
       <c r="E325" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.45">
@@ -7882,7 +7876,7 @@
         <v>790</v>
       </c>
       <c r="E326" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.45">
@@ -7896,7 +7890,7 @@
         <v>792</v>
       </c>
       <c r="E327" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.45">
@@ -7910,7 +7904,7 @@
         <v>794</v>
       </c>
       <c r="E328" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.45">
@@ -7924,7 +7918,7 @@
         <v>796</v>
       </c>
       <c r="E329" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.45">
@@ -7938,7 +7932,7 @@
         <v>798</v>
       </c>
       <c r="E330" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.45">
@@ -7952,7 +7946,7 @@
         <v>800</v>
       </c>
       <c r="E331" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.45">
@@ -7966,7 +7960,7 @@
         <v>802</v>
       </c>
       <c r="E332" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.45">
@@ -7980,7 +7974,7 @@
         <v>804</v>
       </c>
       <c r="E333" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.45">
@@ -7994,7 +7988,7 @@
         <v>806</v>
       </c>
       <c r="E334" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.45">
@@ -8008,7 +8002,7 @@
         <v>808</v>
       </c>
       <c r="E335" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.45">
@@ -8022,7 +8016,7 @@
         <v>810</v>
       </c>
       <c r="E336" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.45">
@@ -8036,7 +8030,7 @@
         <v>812</v>
       </c>
       <c r="E337" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.45">
@@ -8050,7 +8044,7 @@
         <v>814</v>
       </c>
       <c r="E338" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.45">
@@ -8064,7 +8058,7 @@
         <v>816</v>
       </c>
       <c r="E339" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.45">
@@ -8078,7 +8072,7 @@
         <v>818</v>
       </c>
       <c r="E340" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.45">
@@ -8092,7 +8086,7 @@
         <v>820</v>
       </c>
       <c r="E341" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.45">
@@ -8106,7 +8100,7 @@
         <v>822</v>
       </c>
       <c r="E342" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.45">
@@ -8120,7 +8114,7 @@
         <v>824</v>
       </c>
       <c r="E343" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.45">
@@ -8134,7 +8128,7 @@
         <v>826</v>
       </c>
       <c r="E344" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.45">
@@ -8148,7 +8142,7 @@
         <v>828</v>
       </c>
       <c r="E345" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.45">
@@ -8162,7 +8156,7 @@
         <v>830</v>
       </c>
       <c r="E346" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.45">
@@ -8176,7 +8170,7 @@
         <v>832</v>
       </c>
       <c r="E347" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.45">
@@ -8190,7 +8184,7 @@
         <v>834</v>
       </c>
       <c r="E348" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.45">
@@ -8204,7 +8198,7 @@
         <v>836</v>
       </c>
       <c r="E349" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.45">
@@ -8218,7 +8212,7 @@
         <v>838</v>
       </c>
       <c r="E350" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.45">
@@ -8232,7 +8226,7 @@
         <v>840</v>
       </c>
       <c r="E351" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.45">
@@ -8246,7 +8240,7 @@
         <v>842</v>
       </c>
       <c r="E352" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.45">
@@ -8260,7 +8254,7 @@
         <v>844</v>
       </c>
       <c r="E353" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.45">
@@ -8274,7 +8268,7 @@
         <v>846</v>
       </c>
       <c r="E354" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.45">
@@ -8288,7 +8282,7 @@
         <v>848</v>
       </c>
       <c r="E355" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.45">
@@ -8302,7 +8296,7 @@
         <v>850</v>
       </c>
       <c r="E356" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.45">
@@ -8316,7 +8310,7 @@
         <v>852</v>
       </c>
       <c r="E357" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.45">
@@ -8330,7 +8324,7 @@
         <v>854</v>
       </c>
       <c r="E358" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.45">
@@ -8344,7 +8338,7 @@
         <v>856</v>
       </c>
       <c r="E359" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.45">
@@ -8358,7 +8352,7 @@
         <v>858</v>
       </c>
       <c r="E360" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.45">
@@ -8372,7 +8366,7 @@
         <v>860</v>
       </c>
       <c r="E361" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.45">
@@ -8386,7 +8380,7 @@
         <v>862</v>
       </c>
       <c r="E362" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.45">
@@ -8400,7 +8394,7 @@
         <v>864</v>
       </c>
       <c r="E363" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.45">
@@ -8414,7 +8408,7 @@
         <v>866</v>
       </c>
       <c r="E364" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.45">
@@ -8428,7 +8422,7 @@
         <v>868</v>
       </c>
       <c r="E365" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.45">
@@ -8442,7 +8436,7 @@
         <v>870</v>
       </c>
       <c r="E366" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.45">
@@ -8456,7 +8450,7 @@
         <v>872</v>
       </c>
       <c r="E367" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.45">
@@ -8470,7 +8464,7 @@
         <v>874</v>
       </c>
       <c r="E368" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.45">
@@ -8484,7 +8478,7 @@
         <v>876</v>
       </c>
       <c r="E369" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.45">
@@ -8498,7 +8492,7 @@
         <v>878</v>
       </c>
       <c r="E370" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.45">
@@ -8512,7 +8506,7 @@
         <v>880</v>
       </c>
       <c r="E371" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.45">
@@ -8526,7 +8520,7 @@
         <v>882</v>
       </c>
       <c r="E372" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.45">
@@ -8540,7 +8534,7 @@
         <v>884</v>
       </c>
       <c r="E373" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.45">
@@ -8554,7 +8548,7 @@
         <v>886</v>
       </c>
       <c r="E374" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.45">
@@ -8568,7 +8562,7 @@
         <v>888</v>
       </c>
       <c r="E375" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.45">
@@ -8582,7 +8576,7 @@
         <v>890</v>
       </c>
       <c r="E376" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.45">
@@ -8596,7 +8590,7 @@
         <v>892</v>
       </c>
       <c r="E377" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.45">
@@ -8610,7 +8604,7 @@
         <v>894</v>
       </c>
       <c r="E378" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.45">
@@ -8624,7 +8618,7 @@
         <v>896</v>
       </c>
       <c r="E379" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.45">
@@ -8638,7 +8632,7 @@
         <v>898</v>
       </c>
       <c r="E380" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.45">
@@ -8652,7 +8646,7 @@
         <v>900</v>
       </c>
       <c r="E381" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.45">
@@ -8666,7 +8660,7 @@
         <v>902</v>
       </c>
       <c r="E382" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.45">
@@ -8680,7 +8674,7 @@
         <v>904</v>
       </c>
       <c r="E383" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.45">
@@ -8694,7 +8688,7 @@
         <v>906</v>
       </c>
       <c r="E384" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.45">
@@ -8708,7 +8702,7 @@
         <v>908</v>
       </c>
       <c r="E385" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.45">
@@ -8722,7 +8716,7 @@
         <v>910</v>
       </c>
       <c r="E386" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.45">
@@ -8736,7 +8730,7 @@
         <v>912</v>
       </c>
       <c r="E387" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.45">
@@ -8750,7 +8744,7 @@
         <v>914</v>
       </c>
       <c r="E388" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.45">
@@ -8764,7 +8758,7 @@
         <v>916</v>
       </c>
       <c r="E389" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.45">
@@ -8778,7 +8772,7 @@
         <v>918</v>
       </c>
       <c r="E390" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.45">
@@ -8792,7 +8786,7 @@
         <v>920</v>
       </c>
       <c r="E391" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.45">
@@ -8806,7 +8800,7 @@
         <v>922</v>
       </c>
       <c r="E392" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.45">
@@ -8820,7 +8814,7 @@
         <v>924</v>
       </c>
       <c r="E393" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.45">
@@ -8834,7 +8828,7 @@
         <v>926</v>
       </c>
       <c r="E394" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.45">
@@ -8848,7 +8842,7 @@
         <v>928</v>
       </c>
       <c r="E395" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.45">
@@ -8862,7 +8856,7 @@
         <v>930</v>
       </c>
       <c r="E396" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.45">
@@ -8876,7 +8870,7 @@
         <v>932</v>
       </c>
       <c r="E397" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.45">
@@ -8890,7 +8884,7 @@
         <v>934</v>
       </c>
       <c r="E398" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.45">
@@ -8904,7 +8898,7 @@
         <v>936</v>
       </c>
       <c r="E399" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.45">
@@ -8918,7 +8912,7 @@
         <v>938</v>
       </c>
       <c r="E400" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.45">
@@ -8932,7 +8926,7 @@
         <v>940</v>
       </c>
       <c r="E401" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -8941,7 +8935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718D7FD7-C83A-40FD-B4D1-09885A1486FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8957,561 +8951,561 @@
     <col min="10" max="10" width="24.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="H2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="J7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
         <v>96</v>
       </c>
-      <c r="B16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" t="s">
-        <v>103</v>
-      </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D19" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D20" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D21" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" t="s">
         <v>118</v>
-      </c>
-      <c r="F22" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
         <v>120</v>
       </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>121</v>
-      </c>
-      <c r="G23" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
         <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F26" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G26" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="I27" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="H34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="F41" s="3" t="str">
         <f>LEFT(B41,9)</f>
@@ -9520,25 +9514,25 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f t="shared" ref="F42:F43" si="0">LEFT(B42,9)</f>
+        <f>LEFT(B42,9)</f>
         <v>distr_won</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(B43,9)</f>
         <v>distr_wof</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D44" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="F44" s="3" t="str">
         <f>"hs_"&amp;D44</f>
@@ -9547,28 +9541,28 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D45" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f t="shared" ref="F45:F47" si="1">"hs_"&amp;D45</f>
+        <f>"hs_"&amp;D45</f>
         <v>hs_hydro</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>"hs_"&amp;D46</f>
         <v>hs_nuclear</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D47" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>"hs_"&amp;D47</f>
         <v>hs_coal</v>
       </c>
     </row>

--- a/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
+++ b/VerveStacks_CHN_grids_kan60/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A7356E-2A90-4562-8F12-BDF2EB772E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CA3BF4-AF02-415D-9C1A-3895516C677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
